--- a/data/raw/GLNPO 2024 Spring/Erie/D100/ER 63 D100 Spring 202424GE00I33 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Erie/D100/ER 63 D100 Spring 202424GE00I33 Zoop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Erie\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBA70FB-6669-428B-8CED-B5451982B078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CC2803-EE65-41BF-9C15-EC6A90750BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5EC08AF0-3BF1-4A72-9C0A-B465BE7095BF}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="45" r:id="rId2"/>
+    <pivotCache cacheId="11" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4498,7 +4498,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{94D0AD5D-9AD0-4F8A-B5BC-0E7B4216228B}" name="PivotTable1" cacheId="45" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{94D0AD5D-9AD0-4F8A-B5BC-0E7B4216228B}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="U2:Z19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -14505,7 +14505,7 @@
         <v>64</v>
       </c>
       <c r="F175" s="6">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="G175" s="6" t="s">
         <v>22</v>
@@ -14558,7 +14558,7 @@
         <v>21</v>
       </c>
       <c r="F176" s="6">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="G176" s="6" t="s">
         <v>22</v>
@@ -14611,7 +14611,7 @@
         <v>61</v>
       </c>
       <c r="F177" s="6">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="G177" s="6" t="s">
         <v>22</v>
@@ -14717,7 +14717,7 @@
         <v>64</v>
       </c>
       <c r="F179" s="6">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="G179" s="6" t="s">
         <v>22</v>
@@ -14823,7 +14823,7 @@
         <v>64</v>
       </c>
       <c r="F181" s="6">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="G181" s="6" t="s">
         <v>22</v>
@@ -14876,7 +14876,7 @@
         <v>21</v>
       </c>
       <c r="F182" s="6">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="G182" s="6" t="s">
         <v>22</v>
@@ -14929,7 +14929,7 @@
         <v>61</v>
       </c>
       <c r="F183" s="6">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="G183" s="6" t="s">
         <v>22</v>
@@ -15035,7 +15035,7 @@
         <v>64</v>
       </c>
       <c r="F185" s="6">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="G185" s="6" t="s">
         <v>22</v>
